--- a/artfynd/A 26687-2025 artfynd.xlsx
+++ b/artfynd/A 26687-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1172,6 +1172,466 @@
           <t>Hälsinglands flora (2019)</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127742231</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sundsberget, Segersta, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>592072</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6792231</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Segersta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 blomstängel, minst 17 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127742243</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sundsberget, Segersta, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>592043</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6792246</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Segersta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2 blomstänglar, minst 10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127742199</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sundsberget, Segersta, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>592057</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6792597</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Segersta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 blomstängel, minst 25 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127742283</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sundsberget, Segersta, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>592046</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6792242</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Segersta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 blomstängel, minst 11 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Helena Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26687-2025 artfynd.xlsx
+++ b/artfynd/A 26687-2025 artfynd.xlsx
@@ -1405,7 +1405,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127742199</v>
+        <v>127742283</v>
       </c>
       <c r="B8" t="n">
         <v>98450</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592057</v>
+        <v>592046</v>
       </c>
       <c r="R8" t="n">
-        <v>6792597</v>
+        <v>6792242</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 blomstängel, minst 25 bladrosetter</t>
+          <t>1 blomstängel, minst 11 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,7 +1520,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127742283</v>
+        <v>127742199</v>
       </c>
       <c r="B9" t="n">
         <v>98450</v>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592046</v>
+        <v>592057</v>
       </c>
       <c r="R9" t="n">
-        <v>6792242</v>
+        <v>6792597</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 blomstängel, minst 11 bladrosetter</t>
+          <t>1 blomstängel, minst 25 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26687-2025 artfynd.xlsx
+++ b/artfynd/A 26687-2025 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>127742231</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>127742243</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>127742283</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>127742199</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26687-2025 artfynd.xlsx
+++ b/artfynd/A 26687-2025 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>127742231</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>127742243</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>127742283</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>127742199</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26687-2025 artfynd.xlsx
+++ b/artfynd/A 26687-2025 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>127742231</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>127742243</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>127742283</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>127742199</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26687-2025 artfynd.xlsx
+++ b/artfynd/A 26687-2025 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>127742231</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>127742243</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,10 +1405,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127742283</v>
+        <v>127742199</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592046</v>
+        <v>592057</v>
       </c>
       <c r="R8" t="n">
-        <v>6792242</v>
+        <v>6792597</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 blomstängel, minst 11 bladrosetter</t>
+          <t>1 blomstängel, minst 25 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,10 +1520,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127742199</v>
+        <v>127742283</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592057</v>
+        <v>592046</v>
       </c>
       <c r="R9" t="n">
-        <v>6792597</v>
+        <v>6792242</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 blomstängel, minst 25 bladrosetter</t>
+          <t>1 blomstängel, minst 11 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26687-2025 artfynd.xlsx
+++ b/artfynd/A 26687-2025 artfynd.xlsx
@@ -1405,7 +1405,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127742199</v>
+        <v>127742283</v>
       </c>
       <c r="B8" t="n">
         <v>98468</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1452,10 +1452,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592057</v>
+        <v>592046</v>
       </c>
       <c r="R8" t="n">
-        <v>6792597</v>
+        <v>6792242</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 blomstängel, minst 25 bladrosetter</t>
+          <t>1 blomstängel, minst 11 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1520,7 +1520,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127742283</v>
+        <v>127742199</v>
       </c>
       <c r="B9" t="n">
         <v>98468</v>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1567,10 +1567,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592046</v>
+        <v>592057</v>
       </c>
       <c r="R9" t="n">
-        <v>6792242</v>
+        <v>6792597</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 blomstängel, minst 11 bladrosetter</t>
+          <t>1 blomstängel, minst 25 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26687-2025 artfynd.xlsx
+++ b/artfynd/A 26687-2025 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>127742231</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>127742243</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>127742283</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>127742199</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26687-2025 artfynd.xlsx
+++ b/artfynd/A 26687-2025 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>127742231</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>127742243</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>127742283</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>127742199</v>
       </c>
       <c r="B9" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 26687-2025 artfynd.xlsx
+++ b/artfynd/A 26687-2025 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>127742231</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>127742243</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>127742283</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>127742199</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
